--- a/artfynd/A 25553-2026 artfynd.xlsx
+++ b/artfynd/A 25553-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135897784</v>
       </c>
       <c r="B2" t="n">
-        <v>109986</v>
+        <v>110009</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 25553-2026 artfynd.xlsx
+++ b/artfynd/A 25553-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135897784</v>
       </c>
       <c r="B2" t="n">
-        <v>110009</v>
+        <v>110011</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 25553-2026 artfynd.xlsx
+++ b/artfynd/A 25553-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135897784</v>
       </c>
       <c r="B2" t="n">
-        <v>110012</v>
+        <v>110013</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 25553-2026 artfynd.xlsx
+++ b/artfynd/A 25553-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135897784</v>
       </c>
       <c r="B2" t="n">
-        <v>110013</v>
+        <v>110019</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 25553-2026 artfynd.xlsx
+++ b/artfynd/A 25553-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135897784</v>
       </c>
       <c r="B2" t="n">
-        <v>110019</v>
+        <v>110020</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
